--- a/data/trans_bre/P19C01-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P19C01-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 2,93</t>
+          <t>-5,31; 3,37</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,0; 9,26</t>
+          <t>1,93; 9,48</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,34; 12,19</t>
+          <t>1,03; 12,15</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 9,19</t>
+          <t>-1,29; 8,64</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-21,27; 14,39</t>
+          <t>-20,64; 16,19</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,14; 60,09</t>
+          <t>9,93; 61,32</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,44; 49,04</t>
+          <t>3,13; 50,01</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 26,95</t>
+          <t>-3,33; 24,91</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,18; 9,32</t>
+          <t>2,16; 9,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,79; 8,35</t>
+          <t>2,22; 8,95</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 6,22</t>
+          <t>-0,52; 6,46</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-8,72; 21,25</t>
+          <t>-8,11; 22,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,49; 33,79</t>
+          <t>6,98; 32,54</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,57; 27,78</t>
+          <t>6,85; 29,79</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 15,72</t>
+          <t>-1,21; 16,19</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-14,83; 50,01</t>
+          <t>-13,61; 54,31</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,97; 6,1</t>
+          <t>-7,32; 5,6</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,95; 18,45</t>
+          <t>4,33; 19,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,12; 7,52</t>
+          <t>-5,23; 7,68</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,12; 3,86</t>
+          <t>-6,18; 4,07</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-18,6; 15,93</t>
+          <t>-17,16; 15,49</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,43; 46,47</t>
+          <t>9,4; 48,94</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-9,54; 15,82</t>
+          <t>-9,87; 15,95</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,54; 5,86</t>
+          <t>-8,67; 6,31</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 4,38</t>
+          <t>-0,92; 4,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,37; 7,44</t>
+          <t>2,41; 7,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 5,4</t>
+          <t>0,12; 5,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,86; 13,62</t>
+          <t>-5,96; 12,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 15,35</t>
+          <t>-2,99; 14,75</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,59; 26,14</t>
+          <t>7,93; 25,77</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 13,51</t>
+          <t>0,29; 13,27</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-10,15; 30,04</t>
+          <t>-10,32; 29,12</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P19C01-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P19C01-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,7</t>
+          <t>5,41</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>14,78%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,31; 3,37</t>
+          <t>-5,13; 3,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,93; 9,48</t>
+          <t>1,89; 9,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,03; 12,15</t>
+          <t>0,77; 12,05</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 8,64</t>
+          <t>1,01; 10,78</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-20,64; 16,19</t>
+          <t>-19,71; 15,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,93; 61,32</t>
+          <t>8,81; 60,72</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,13; 50,01</t>
+          <t>3,17; 50,32</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 24,91</t>
+          <t>2,62; 33,1</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4,81</t>
+          <t>4,36</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>7,47%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,16; 9,08</t>
+          <t>2,02; 9,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,22; 8,95</t>
+          <t>2,2; 8,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 6,46</t>
+          <t>-0,57; 6,27</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-8,11; 22,02</t>
+          <t>1,5; 7,82</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,98; 32,54</t>
+          <t>6,42; 32,36</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,85; 29,79</t>
+          <t>6,66; 29,37</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 16,19</t>
+          <t>-1,36; 15,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-13,61; 54,31</t>
+          <t>2,55; 14,02</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-1,31</t>
+          <t>-1,54</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-1,91%</t>
+          <t>-2,24%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,32; 5,6</t>
+          <t>-8,4; 5,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,33; 19,12</t>
+          <t>4,04; 18,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,23; 7,68</t>
+          <t>-5,78; 7,65</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,18; 4,07</t>
+          <t>-7,0; 3,08</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-17,16; 15,49</t>
+          <t>-18,84; 14,85</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,4; 48,94</t>
+          <t>8,29; 48,03</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-9,87; 15,95</t>
+          <t>-10,57; 16,21</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,67; 6,31</t>
+          <t>-9,81; 4,71</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,5</t>
+          <t>2,07</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 4,24</t>
+          <t>-0,99; 4,32</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,41; 7,2</t>
+          <t>2,22; 7,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,12; 5,19</t>
+          <t>0,02; 5,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,96; 12,91</t>
+          <t>-0,31; 4,41</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 14,75</t>
+          <t>-3,12; 15,26</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,93; 25,77</t>
+          <t>7,13; 25,16</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,29; 13,27</t>
+          <t>0,06; 13,72</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-10,32; 29,12</t>
+          <t>-0,55; 7,9</t>
         </is>
       </c>
     </row>
